--- a/ALBION_Biomarkers.xlsx
+++ b/ALBION_Biomarkers.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20325" windowHeight="9600"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Biomarkers" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="144">
   <si>
     <t>ID</t>
   </si>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>Targeted metabolomics analysis</t>
-  </si>
-  <si>
-    <t>Biomarkers Neurodegeneration-plasma</t>
   </si>
   <si>
     <t>Inflammation- blood</t>
@@ -189,12 +186,6 @@
   </si>
   <si>
     <t>Intake of macro- and micronutrients and food groups across the day and per 2-hour intervals; adherence to dietary patterns (Mediterranean diet, MIND diet); breakfast and dinner consumption and other meal habits; recording of other dietary habits/behaviors (e.g., fermented foods, ultra-processed foods, dietary diversity, variety of vegetables and fruits).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Includes traditional MRI sequences and collects information on brain structure - atrophy, communication (DTI), function (resting BOLD)  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRI at a follow-up visit-Includes traditional MRI sequences and collects information on brain structure - atrophy, communication (DTI), function (resting BOLD)  </t>
   </si>
   <si>
     <t>Oxidative Stress Markers-CSF</t>
@@ -456,6 +447,21 @@
   </si>
   <si>
     <t>Biomarkers Neurodegeneration-CSF follow-up</t>
+  </si>
+  <si>
+    <t>If MRI is performed</t>
+  </si>
+  <si>
+    <t>If MRI is re-performed at a follow-up visit</t>
+  </si>
+  <si>
+    <t>If EEG is performed</t>
+  </si>
+  <si>
+    <t>If EEG is re-performed at a follow-up visit</t>
+  </si>
+  <si>
+    <t>Biomarkers Neurodegeneration-blood</t>
   </si>
 </sst>
 </file>
@@ -1250,31 +1256,31 @@
         <v>2</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E1" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="53" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="H1" s="53" t="s">
-        <v>124</v>
-      </c>
       <c r="I1" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="J1" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="J1" s="53" t="s">
-        <v>133</v>
-      </c>
       <c r="K1" s="53" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L1" s="53" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="M1" s="19" t="s">
         <v>20</v>
@@ -1283,28 +1289,28 @@
         <v>21</v>
       </c>
       <c r="O1" s="53" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P1" s="53" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q1" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="R1" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="S1" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="53" t="s">
-        <v>141</v>
-      </c>
-      <c r="S1" s="19" t="s">
+      <c r="T1" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="U1" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="V1" s="19" t="s">
         <v>41</v>
-      </c>
-      <c r="V1" s="19" t="s">
-        <v>42</v>
       </c>
       <c r="W1" s="19" t="s">
         <v>4</v>
@@ -1328,7 +1334,7 @@
         <v>10</v>
       </c>
       <c r="AD1" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE1" s="19" t="s">
         <v>11</v>
@@ -1343,10 +1349,10 @@
         <v>14</v>
       </c>
       <c r="AI1" s="57" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="AJ1" s="37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="AK1" s="19" t="s">
         <v>15</v>
@@ -1735,7 +1741,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D5" s="39">
         <v>1</v>
@@ -1820,7 +1826,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D6" s="61">
         <v>3</v>
@@ -1923,7 +1929,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D7" s="39">
         <v>2</v>
@@ -2024,7 +2030,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D8" s="39">
         <v>2</v>
@@ -2105,7 +2111,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D9" s="39">
         <v>2</v>
@@ -2196,7 +2202,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D10" s="39">
         <v>3</v>
@@ -2301,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D11" s="39">
         <v>1</v>
@@ -2394,7 +2400,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D12" s="39">
         <v>2</v>
@@ -2493,7 +2499,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D13" s="39">
         <v>2</v>
@@ -2574,7 +2580,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" s="39">
         <v>1</v>
@@ -2651,7 +2657,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D15" s="39">
         <v>2</v>
@@ -2736,7 +2742,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D16" s="61">
         <v>3</v>
@@ -2841,7 +2847,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D17" s="61">
         <v>2</v>
@@ -2942,7 +2948,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D18" s="39">
         <v>2</v>
@@ -3029,7 +3035,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D19" s="39">
         <v>3</v>
@@ -3124,7 +3130,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D20" s="39">
         <v>2</v>
@@ -3215,7 +3221,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D21" s="39">
         <v>3</v>
@@ -3322,7 +3328,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D22" s="61">
         <v>2</v>
@@ -3431,7 +3437,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D23" s="39">
         <v>3</v>
@@ -3530,7 +3536,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D24" s="39">
         <v>1</v>
@@ -3607,7 +3613,7 @@
         <v>6</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D25" s="39">
         <v>3</v>
@@ -3712,7 +3718,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D26" s="39">
         <v>1</v>
@@ -3791,7 +3797,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D27" s="61">
         <v>2</v>
@@ -3888,7 +3894,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D28" s="39">
         <v>1</v>
@@ -3967,7 +3973,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="39" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D29" s="39">
         <v>2</v>
@@ -4078,7 +4084,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D30" s="39">
         <v>1</v>
@@ -4157,7 +4163,7 @@
         <v>6</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D31" s="61">
         <v>3</v>
@@ -4270,7 +4276,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="61" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D32" s="61">
         <v>3</v>
@@ -4379,7 +4385,7 @@
         <v>6</v>
       </c>
       <c r="C33" s="39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D33" s="39">
         <v>3</v>
@@ -4484,7 +4490,7 @@
         <v>6</v>
       </c>
       <c r="C34" s="39" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D34" s="39">
         <v>3</v>
@@ -4571,7 +4577,7 @@
         <v>4</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D35" s="39">
         <v>2</v>
@@ -4664,7 +4670,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="61" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D36" s="61">
         <v>3</v>
@@ -4775,7 +4781,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D37" s="39">
         <v>3</v>
@@ -4884,7 +4890,7 @@
         <v>6</v>
       </c>
       <c r="C38" s="39" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D38" s="39">
         <v>3</v>
@@ -4995,7 +5001,7 @@
         <v>6</v>
       </c>
       <c r="C39" s="39" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D39" s="39">
         <v>3</v>
@@ -5110,7 +5116,7 @@
         <v>4</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D40" s="39">
         <v>1</v>
@@ -5187,7 +5193,7 @@
         <v>6</v>
       </c>
       <c r="C41" s="61" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D41" s="61">
         <v>3</v>
@@ -5304,7 +5310,7 @@
         <v>6</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D42" s="39">
         <v>3</v>
@@ -5415,7 +5421,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D43" s="39">
         <v>1</v>
@@ -5597,7 +5603,7 @@
         <v>6</v>
       </c>
       <c r="C45" s="61" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D45" s="61">
         <v>4</v>
@@ -5712,7 +5718,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="39" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D46" s="39">
         <v>1</v>
@@ -5791,7 +5797,7 @@
         <v>3</v>
       </c>
       <c r="C47" s="39" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D47" s="39">
         <v>2</v>
@@ -5955,7 +5961,7 @@
         <v>3</v>
       </c>
       <c r="C49" s="39" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D49" s="39">
         <v>1</v>
@@ -6034,7 +6040,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D50" s="39">
         <v>2</v>
@@ -6135,7 +6141,7 @@
         <v>5</v>
       </c>
       <c r="C51" s="61" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D51" s="61">
         <v>1</v>
@@ -6440,7 +6446,7 @@
         <v>3</v>
       </c>
       <c r="C54" s="39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D54" s="39">
         <v>2</v>
@@ -6533,7 +6539,7 @@
         <v>2</v>
       </c>
       <c r="C55" s="39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D55" s="39">
         <v>1</v>
@@ -6966,7 +6972,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D60" s="39">
         <v>3</v>
@@ -7152,7 +7158,7 @@
         <v>4</v>
       </c>
       <c r="C62" s="39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D62" s="39">
         <v>2</v>
@@ -7253,7 +7259,7 @@
         <v>3</v>
       </c>
       <c r="C63" s="39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D63" s="39">
         <v>1</v>
@@ -7330,7 +7336,7 @@
         <v>5</v>
       </c>
       <c r="C64" s="39" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D64" s="39">
         <v>3</v>
@@ -7431,7 +7437,7 @@
         <v>2</v>
       </c>
       <c r="C65" s="39" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D65" s="39">
         <v>1</v>
@@ -7633,7 +7639,7 @@
         <v>4</v>
       </c>
       <c r="C67" s="61" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D67" s="61">
         <v>2</v>
@@ -7738,7 +7744,7 @@
         <v>5</v>
       </c>
       <c r="C68" s="39" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D68" s="39">
         <v>3</v>
@@ -7851,7 +7857,7 @@
         <v>5</v>
       </c>
       <c r="C69" s="39" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D69" s="39">
         <v>3</v>
@@ -7966,7 +7972,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D70" s="39">
         <v>3</v>
@@ -8079,7 +8085,7 @@
         <v>5</v>
       </c>
       <c r="C71" s="39" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D71" s="39">
         <v>3</v>
@@ -8188,7 +8194,7 @@
         <v>4</v>
       </c>
       <c r="C72" s="61" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D72" s="61">
         <v>2</v>
@@ -8285,7 +8291,7 @@
         <v>4</v>
       </c>
       <c r="C73" s="39" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D73" s="39">
         <v>3</v>
@@ -8388,7 +8394,7 @@
         <v>5</v>
       </c>
       <c r="C74" s="39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D74" s="39">
         <v>2</v>
@@ -8489,7 +8495,7 @@
         <v>4</v>
       </c>
       <c r="C75" s="39" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D75" s="39">
         <v>1</v>
@@ -8598,7 +8604,7 @@
         <v>3</v>
       </c>
       <c r="C76" s="39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D76" s="39">
         <v>2</v>
@@ -8863,7 +8869,7 @@
         <v>4</v>
       </c>
       <c r="C79" s="61" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D79" s="61">
         <v>3</v>
@@ -8980,7 +8986,7 @@
         <v>4</v>
       </c>
       <c r="C80" s="39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D80" s="39">
         <v>3</v>
@@ -9077,7 +9083,7 @@
         <v>3</v>
       </c>
       <c r="C81" s="39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D81" s="39">
         <v>2</v>
@@ -9182,7 +9188,7 @@
         <v>5</v>
       </c>
       <c r="C82" s="39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D82" s="39">
         <v>3</v>
@@ -9283,7 +9289,7 @@
         <v>4</v>
       </c>
       <c r="C83" s="39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D83" s="39">
         <v>3</v>
@@ -9380,7 +9386,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D84" s="39">
         <v>1</v>
@@ -9471,7 +9477,7 @@
         <v>4</v>
       </c>
       <c r="C85" s="39" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D85" s="39">
         <v>3</v>
@@ -9582,7 +9588,7 @@
         <v>5</v>
       </c>
       <c r="C86" s="39" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D86" s="39">
         <v>2</v>
@@ -9685,7 +9691,7 @@
         <v>3</v>
       </c>
       <c r="C87" s="39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D87" s="39">
         <v>2</v>
@@ -9782,7 +9788,7 @@
         <v>5</v>
       </c>
       <c r="C88" s="39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D88" s="39">
         <v>2</v>
@@ -9891,7 +9897,7 @@
         <v>3</v>
       </c>
       <c r="C89" s="39" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D89" s="39">
         <v>1</v>
@@ -10055,7 +10061,7 @@
         <v>2</v>
       </c>
       <c r="C91" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D91" s="39">
         <v>1</v>
@@ -10140,7 +10146,7 @@
         <v>4</v>
       </c>
       <c r="C92" s="39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D92" s="39">
         <v>3</v>
@@ -10334,7 +10340,7 @@
         <v>4</v>
       </c>
       <c r="C94" s="39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D94" s="39">
         <v>2</v>
@@ -10433,7 +10439,7 @@
         <v>3</v>
       </c>
       <c r="C95" s="39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D95" s="39">
         <v>2</v>
@@ -10627,7 +10633,7 @@
         <v>4</v>
       </c>
       <c r="C97" s="39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D97" s="39">
         <v>2</v>
@@ -10736,7 +10742,7 @@
         <v>4</v>
       </c>
       <c r="C98" s="39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D98" s="39">
         <v>2</v>
@@ -10841,7 +10847,7 @@
         <v>4</v>
       </c>
       <c r="C99" s="39" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D99" s="39">
         <v>2</v>
@@ -10948,7 +10954,7 @@
         <v>4</v>
       </c>
       <c r="C100" s="39" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D100" s="39">
         <v>2</v>
@@ -11227,7 +11233,7 @@
         <v>4</v>
       </c>
       <c r="C103" s="39" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D103" s="39">
         <v>2</v>
@@ -11336,7 +11342,7 @@
         <v>4</v>
       </c>
       <c r="C104" s="39" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D104" s="39">
         <v>2</v>
@@ -11429,7 +11435,7 @@
         <v>3</v>
       </c>
       <c r="C105" s="39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D105" s="39">
         <v>2</v>
@@ -11633,7 +11639,7 @@
         <v>3</v>
       </c>
       <c r="C107" s="39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D107" s="39">
         <v>2</v>
@@ -11744,7 +11750,7 @@
         <v>3</v>
       </c>
       <c r="C108" s="39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D108" s="39">
         <v>2</v>
@@ -11825,7 +11831,7 @@
         <v>5</v>
       </c>
       <c r="C109" s="39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D109" s="39">
         <v>2</v>
@@ -11930,7 +11936,7 @@
         <v>4</v>
       </c>
       <c r="C110" s="39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D110" s="39">
         <v>2</v>
@@ -12033,7 +12039,7 @@
         <v>3</v>
       </c>
       <c r="C111" s="39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D111" s="39">
         <v>2</v>
@@ -12118,7 +12124,7 @@
         <v>4</v>
       </c>
       <c r="C112" s="39" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D112" s="39">
         <v>2</v>
@@ -12213,7 +12219,7 @@
         <v>5</v>
       </c>
       <c r="C113" s="39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D113" s="39">
         <v>2</v>
@@ -12308,7 +12314,7 @@
         <v>3</v>
       </c>
       <c r="C114" s="39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D114" s="39">
         <v>2</v>
@@ -12411,7 +12417,7 @@
         <v>3</v>
       </c>
       <c r="C115" s="39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D115" s="39">
         <v>2</v>
@@ -12502,7 +12508,7 @@
         <v>4</v>
       </c>
       <c r="C116" s="39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D116" s="39">
         <v>2</v>
@@ -12607,7 +12613,7 @@
         <v>3</v>
       </c>
       <c r="C117" s="39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D117" s="39">
         <v>2</v>
@@ -12716,7 +12722,7 @@
         <v>3</v>
       </c>
       <c r="C118" s="39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D118" s="39">
         <v>2</v>
@@ -12823,7 +12829,7 @@
         <v>4</v>
       </c>
       <c r="C119" s="39" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D119" s="39">
         <v>2</v>
@@ -12930,7 +12936,7 @@
         <v>3</v>
       </c>
       <c r="C120" s="39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D120" s="39">
         <v>1</v>
@@ -13029,7 +13035,7 @@
         <v>3</v>
       </c>
       <c r="C121" s="39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D121" s="39">
         <v>2</v>
@@ -13213,7 +13219,7 @@
         <v>3</v>
       </c>
       <c r="C123" s="39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D123" s="39">
         <v>2</v>
@@ -13413,7 +13419,7 @@
         <v>4</v>
       </c>
       <c r="C125" s="39" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D125" s="39">
         <v>3</v>
@@ -13506,7 +13512,7 @@
         <v>4</v>
       </c>
       <c r="C126" s="39" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D126" s="39">
         <v>3</v>
@@ -13601,7 +13607,7 @@
         <v>4</v>
       </c>
       <c r="C127" s="39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D127" s="39">
         <v>2</v>
@@ -13698,7 +13704,7 @@
         <v>4</v>
       </c>
       <c r="C128" s="39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D128" s="39">
         <v>3</v>
@@ -13890,7 +13896,7 @@
         <v>4</v>
       </c>
       <c r="C130" s="39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D130" s="39">
         <v>3</v>
@@ -14193,7 +14199,7 @@
         <v>4</v>
       </c>
       <c r="C133" s="39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D133" s="39">
         <v>3</v>
@@ -14294,7 +14300,7 @@
         <v>4</v>
       </c>
       <c r="C134" s="39" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D134" s="39">
         <v>3</v>
@@ -14405,7 +14411,7 @@
         <v>3</v>
       </c>
       <c r="C135" s="39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D135" s="39">
         <v>2</v>
@@ -14510,7 +14516,7 @@
         <v>4</v>
       </c>
       <c r="C136" s="39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D136" s="39">
         <v>3</v>
@@ -14617,7 +14623,7 @@
         <v>4</v>
       </c>
       <c r="C137" s="39" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D137" s="39">
         <v>3</v>
@@ -14722,7 +14728,7 @@
         <v>3</v>
       </c>
       <c r="C138" s="39" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D138" s="39">
         <v>2</v>
@@ -14902,7 +14908,7 @@
         <v>4</v>
       </c>
       <c r="C140" s="39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D140" s="39">
         <v>3</v>
@@ -15007,7 +15013,7 @@
         <v>2</v>
       </c>
       <c r="C141" s="39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D141" s="39">
         <v>2</v>
@@ -15092,7 +15098,7 @@
         <v>2</v>
       </c>
       <c r="C142" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D142" s="39">
         <v>1</v>
@@ -15294,7 +15300,7 @@
         <v>3</v>
       </c>
       <c r="C144" s="39" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D144" s="39">
         <v>2</v>
@@ -15371,7 +15377,7 @@
         <v>3</v>
       </c>
       <c r="C145" s="39" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D145" s="39">
         <v>2</v>
@@ -15476,7 +15482,7 @@
         <v>2</v>
       </c>
       <c r="C146" s="39" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D146" s="39">
         <v>2</v>
@@ -15711,7 +15717,7 @@
         <v>4</v>
       </c>
       <c r="C149" s="39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D149" s="39">
         <v>3</v>
@@ -15804,7 +15810,7 @@
         <v>4</v>
       </c>
       <c r="C150" s="39" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D150" s="39">
         <v>3</v>
@@ -16020,7 +16026,7 @@
         <v>4</v>
       </c>
       <c r="C152" s="39" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D152" s="39">
         <v>2</v>
@@ -16295,7 +16301,7 @@
         <v>2</v>
       </c>
       <c r="C155" s="39" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D155" s="39">
         <v>2</v>
@@ -16396,7 +16402,7 @@
         <v>2</v>
       </c>
       <c r="C156" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D156" s="39">
         <v>1</v>
@@ -16673,7 +16679,7 @@
         <v>3</v>
       </c>
       <c r="C159" s="39" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D159" s="39">
         <v>2</v>
@@ -16772,7 +16778,7 @@
         <v>3</v>
       </c>
       <c r="C160" s="39" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D160" s="39">
         <v>3</v>
@@ -16861,7 +16867,7 @@
         <v>2</v>
       </c>
       <c r="C161" s="39" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D161" s="39">
         <v>2</v>
@@ -17213,7 +17219,7 @@
         <v>3</v>
       </c>
       <c r="C165" s="39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D165" s="39">
         <v>1</v>
@@ -17300,7 +17306,7 @@
         <v>3</v>
       </c>
       <c r="C166" s="39" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D166" s="39">
         <v>1</v>
@@ -17381,7 +17387,7 @@
         <v>2</v>
       </c>
       <c r="C167" s="39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D167" s="39">
         <v>1</v>
@@ -17478,7 +17484,7 @@
         <v>2</v>
       </c>
       <c r="C168" s="39" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D168" s="39">
         <v>1</v>
@@ -18243,7 +18249,7 @@
         <v>2</v>
       </c>
       <c r="C177" s="39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D177" s="39">
         <v>1</v>
@@ -18332,7 +18338,7 @@
         <v>2</v>
       </c>
       <c r="C178" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D178" s="39">
         <v>1</v>
@@ -18506,7 +18512,7 @@
         <v>2</v>
       </c>
       <c r="C180" s="39" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D180" s="39">
         <v>1</v>
@@ -18761,7 +18767,7 @@
         <v>2</v>
       </c>
       <c r="C183" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D183" s="39">
         <v>1</v>
@@ -18838,7 +18844,7 @@
         <v>3</v>
       </c>
       <c r="C184" s="39" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D184" s="39">
         <v>2</v>
@@ -19004,7 +19010,7 @@
         <v>3</v>
       </c>
       <c r="C186" s="39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D186" s="39">
         <v>2</v>
@@ -19340,7 +19346,7 @@
         <v>2</v>
       </c>
       <c r="C190" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D190" s="39">
         <v>1</v>
@@ -19609,7 +19615,7 @@
         <v>2</v>
       </c>
       <c r="C193" s="39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D193" s="39">
         <v>1</v>
@@ -19698,7 +19704,7 @@
         <v>2</v>
       </c>
       <c r="C194" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D194" s="39">
         <v>1</v>
@@ -19791,7 +19797,7 @@
         <v>2</v>
       </c>
       <c r="C195" s="39" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D195" s="39">
         <v>1</v>
@@ -19878,7 +19884,7 @@
         <v>2</v>
       </c>
       <c r="C196" s="39" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D196" s="39">
         <v>1</v>
@@ -19965,7 +19971,7 @@
         <v>2</v>
       </c>
       <c r="C197" s="61" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D197" s="61">
         <v>1</v>
@@ -20121,7 +20127,7 @@
         <v>2</v>
       </c>
       <c r="C199" s="39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D199" s="39">
         <v>1</v>
@@ -20210,7 +20216,7 @@
         <v>2</v>
       </c>
       <c r="C200" s="39" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D200" s="39">
         <v>1</v>
@@ -20556,7 +20562,7 @@
         <v>2</v>
       </c>
       <c r="C204" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D204" s="39">
         <v>1</v>
@@ -20726,7 +20732,7 @@
         <v>2</v>
       </c>
       <c r="C206" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D206" s="39">
         <v>1</v>
@@ -20815,7 +20821,7 @@
         <v>2</v>
       </c>
       <c r="C207" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D207" s="39">
         <v>1</v>
@@ -20896,7 +20902,7 @@
         <v>2</v>
       </c>
       <c r="C208" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D208" s="39">
         <v>1</v>
@@ -20985,7 +20991,7 @@
         <v>2</v>
       </c>
       <c r="C209" s="39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D209" s="39">
         <v>1</v>
@@ -21072,7 +21078,7 @@
         <v>2</v>
       </c>
       <c r="C210" s="39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D210" s="39">
         <v>1</v>
@@ -21408,7 +21414,7 @@
         <v>2</v>
       </c>
       <c r="C214" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D214" s="39">
         <v>1</v>
@@ -21499,7 +21505,7 @@
         <v>2</v>
       </c>
       <c r="C215" s="39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D215" s="39">
         <v>1</v>
@@ -21588,7 +21594,7 @@
         <v>2</v>
       </c>
       <c r="C216" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D216" s="39">
         <v>1</v>
@@ -21740,7 +21746,7 @@
         <v>2</v>
       </c>
       <c r="C218" s="39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D218" s="39">
         <v>1</v>
@@ -21829,7 +21835,7 @@
         <v>2</v>
       </c>
       <c r="C219" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D219" s="39">
         <v>1</v>
@@ -22100,7 +22106,7 @@
         <v>2</v>
       </c>
       <c r="C222" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D222" s="39">
         <v>1</v>
@@ -22270,7 +22276,7 @@
         <v>2</v>
       </c>
       <c r="C224" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D224" s="39">
         <v>1</v>
@@ -22758,7 +22764,7 @@
         <v>2</v>
       </c>
       <c r="C230" s="39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D230" s="39">
         <v>1</v>
@@ -22932,7 +22938,7 @@
         <v>2</v>
       </c>
       <c r="C232" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D232" s="39">
         <v>1</v>
@@ -23244,7 +23250,7 @@
         <v>2</v>
       </c>
       <c r="C236" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D236" s="39">
         <v>1</v>
@@ -23477,7 +23483,7 @@
         <v>2</v>
       </c>
       <c r="C239" s="39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D239" s="39">
         <v>1</v>
@@ -23556,7 +23562,7 @@
         <v>2</v>
       </c>
       <c r="C240" s="39" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D240" s="39">
         <v>1</v>
@@ -23645,7 +23651,7 @@
         <v>2</v>
       </c>
       <c r="C241" s="39" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D241" s="39">
         <v>1</v>
@@ -23973,7 +23979,7 @@
         <v>2</v>
       </c>
       <c r="C245" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D245" s="39">
         <v>1</v>
@@ -24271,7 +24277,7 @@
         <v>2</v>
       </c>
       <c r="C249" s="39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D249" s="39">
         <v>1</v>
@@ -24350,7 +24356,7 @@
         <v>2</v>
       </c>
       <c r="C250" s="39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D250" s="39">
         <v>1</v>
@@ -24591,7 +24597,7 @@
         <v>2</v>
       </c>
       <c r="C253" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D253" s="39">
         <v>1</v>
@@ -24676,7 +24682,7 @@
         <v>2</v>
       </c>
       <c r="C254" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D254" s="39">
         <v>1</v>
@@ -24765,7 +24771,7 @@
         <v>2</v>
       </c>
       <c r="C255" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D255" s="39">
         <v>1</v>
@@ -24842,7 +24848,7 @@
         <v>2</v>
       </c>
       <c r="C256" s="39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D256" s="39">
         <v>1</v>
@@ -57502,7 +57508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1009"/>
+  <dimension ref="A1:Z1013"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="64.5703125" customWidth="1"/>
@@ -57512,10 +57518,10 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
@@ -57546,7 +57552,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -57554,7 +57560,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
@@ -57562,369 +57568,370 @@
         <v>1</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="59" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="59" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="59" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="58" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="51"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A16" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="58" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B19" s="58" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="59" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="58" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="10" t="s">
+      <c r="B20" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="10" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="10"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B23" s="10" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B24" s="10"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B29" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="10" t="s">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="10"/>
+    </row>
+    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="30" t="s">
+      <c r="B39" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="32" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="B33" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="10"/>
-    </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B40" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="26" t="s">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="51"/>
-    </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="47"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="33"/>
-      <c r="N41" s="33"/>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="33"/>
-      <c r="S41" s="33"/>
-      <c r="T41" s="33"/>
-      <c r="U41" s="33"/>
-      <c r="V41" s="33"/>
-      <c r="W41" s="33"/>
-      <c r="X41" s="33"/>
-      <c r="Y41" s="33"/>
-      <c r="Z41" s="33"/>
-    </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="47"/>
-      <c r="B42" s="49"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-      <c r="P42" s="33"/>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="33"/>
-      <c r="T42" s="33"/>
-      <c r="U42" s="33"/>
-      <c r="V42" s="33"/>
-      <c r="W42" s="33"/>
-      <c r="X42" s="33"/>
-      <c r="Y42" s="33"/>
-      <c r="Z42" s="33"/>
-    </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="46"/>
-      <c r="B43" s="46"/>
-    </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-    </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-    </row>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
+    </row>
+    <row r="44" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="47"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
+      <c r="M45" s="33"/>
+      <c r="N45" s="33"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
+      <c r="S45" s="33"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="33"/>
+      <c r="V45" s="33"/>
+      <c r="W45" s="33"/>
+      <c r="X45" s="33"/>
+      <c r="Y45" s="33"/>
+      <c r="Z45" s="33"/>
+    </row>
+    <row r="46" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="47"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="50"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="33"/>
+      <c r="M46" s="33"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="33"/>
+      <c r="Y46" s="33"/>
+      <c r="Z46" s="33"/>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
+      <c r="A47" s="46"/>
+      <c r="B47" s="46"/>
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
@@ -61773,6 +61780,22 @@
     <row r="1009" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="10"/>
       <c r="B1009" s="10"/>
+    </row>
+    <row r="1010" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1010" s="10"/>
+      <c r="B1010" s="10"/>
+    </row>
+    <row r="1011" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1011" s="10"/>
+      <c r="B1011" s="10"/>
+    </row>
+    <row r="1012" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1012" s="10"/>
+      <c r="B1012" s="10"/>
+    </row>
+    <row r="1013" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1013" s="10"/>
+      <c r="B1013" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
